--- a/Nigeria/Audience Analysis/Audience Comments - Final/Agba John Doe_Never Leave Marriage Because Husband Cheated.xlsx
+++ b/Nigeria/Audience Analysis/Audience Comments - Final/Agba John Doe_Never Leave Marriage Because Husband Cheated.xlsx
@@ -14,11 +14,551 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="536">
+  <si>
+    <t>Segment ID</t>
+  </si>
   <si>
     <t>text</t>
   </si>
   <si>
+    <t>Source URL</t>
+  </si>
+  <si>
+    <t>Reference Text/Context</t>
+  </si>
+  <si>
+    <t>AGB_001</t>
+  </si>
+  <si>
+    <t>AGB_002</t>
+  </si>
+  <si>
+    <t>AGB_003</t>
+  </si>
+  <si>
+    <t>AGB_004</t>
+  </si>
+  <si>
+    <t>AGB_005</t>
+  </si>
+  <si>
+    <t>AGB_006</t>
+  </si>
+  <si>
+    <t>AGB_007</t>
+  </si>
+  <si>
+    <t>AGB_008</t>
+  </si>
+  <si>
+    <t>AGB_009</t>
+  </si>
+  <si>
+    <t>AGB_010</t>
+  </si>
+  <si>
+    <t>AGB_011</t>
+  </si>
+  <si>
+    <t>AGB_012</t>
+  </si>
+  <si>
+    <t>AGB_013</t>
+  </si>
+  <si>
+    <t>AGB_014</t>
+  </si>
+  <si>
+    <t>AGB_015</t>
+  </si>
+  <si>
+    <t>AGB_016</t>
+  </si>
+  <si>
+    <t>AGB_017</t>
+  </si>
+  <si>
+    <t>AGB_018</t>
+  </si>
+  <si>
+    <t>AGB_019</t>
+  </si>
+  <si>
+    <t>AGB_020</t>
+  </si>
+  <si>
+    <t>AGB_021</t>
+  </si>
+  <si>
+    <t>AGB_022</t>
+  </si>
+  <si>
+    <t>AGB_023</t>
+  </si>
+  <si>
+    <t>AGB_024</t>
+  </si>
+  <si>
+    <t>AGB_025</t>
+  </si>
+  <si>
+    <t>AGB_026</t>
+  </si>
+  <si>
+    <t>AGB_027</t>
+  </si>
+  <si>
+    <t>AGB_028</t>
+  </si>
+  <si>
+    <t>AGB_029</t>
+  </si>
+  <si>
+    <t>AGB_030</t>
+  </si>
+  <si>
+    <t>AGB_031</t>
+  </si>
+  <si>
+    <t>AGB_032</t>
+  </si>
+  <si>
+    <t>AGB_033</t>
+  </si>
+  <si>
+    <t>AGB_034</t>
+  </si>
+  <si>
+    <t>AGB_035</t>
+  </si>
+  <si>
+    <t>AGB_036</t>
+  </si>
+  <si>
+    <t>AGB_037</t>
+  </si>
+  <si>
+    <t>AGB_038</t>
+  </si>
+  <si>
+    <t>AGB_039</t>
+  </si>
+  <si>
+    <t>AGB_040</t>
+  </si>
+  <si>
+    <t>AGB_041</t>
+  </si>
+  <si>
+    <t>AGB_042</t>
+  </si>
+  <si>
+    <t>AGB_043</t>
+  </si>
+  <si>
+    <t>AGB_044</t>
+  </si>
+  <si>
+    <t>AGB_045</t>
+  </si>
+  <si>
+    <t>AGB_046</t>
+  </si>
+  <si>
+    <t>AGB_047</t>
+  </si>
+  <si>
+    <t>AGB_048</t>
+  </si>
+  <si>
+    <t>AGB_049</t>
+  </si>
+  <si>
+    <t>AGB_050</t>
+  </si>
+  <si>
+    <t>AGB_051</t>
+  </si>
+  <si>
+    <t>AGB_052</t>
+  </si>
+  <si>
+    <t>AGB_053</t>
+  </si>
+  <si>
+    <t>AGB_054</t>
+  </si>
+  <si>
+    <t>AGB_055</t>
+  </si>
+  <si>
+    <t>AGB_056</t>
+  </si>
+  <si>
+    <t>AGB_057</t>
+  </si>
+  <si>
+    <t>AGB_058</t>
+  </si>
+  <si>
+    <t>AGB_059</t>
+  </si>
+  <si>
+    <t>AGB_060</t>
+  </si>
+  <si>
+    <t>AGB_061</t>
+  </si>
+  <si>
+    <t>AGB_062</t>
+  </si>
+  <si>
+    <t>AGB_063</t>
+  </si>
+  <si>
+    <t>AGB_064</t>
+  </si>
+  <si>
+    <t>AGB_065</t>
+  </si>
+  <si>
+    <t>AGB_066</t>
+  </si>
+  <si>
+    <t>AGB_067</t>
+  </si>
+  <si>
+    <t>AGB_068</t>
+  </si>
+  <si>
+    <t>AGB_069</t>
+  </si>
+  <si>
+    <t>AGB_070</t>
+  </si>
+  <si>
+    <t>AGB_071</t>
+  </si>
+  <si>
+    <t>AGB_072</t>
+  </si>
+  <si>
+    <t>AGB_073</t>
+  </si>
+  <si>
+    <t>AGB_074</t>
+  </si>
+  <si>
+    <t>AGB_075</t>
+  </si>
+  <si>
+    <t>AGB_076</t>
+  </si>
+  <si>
+    <t>AGB_077</t>
+  </si>
+  <si>
+    <t>AGB_078</t>
+  </si>
+  <si>
+    <t>AGB_079</t>
+  </si>
+  <si>
+    <t>AGB_080</t>
+  </si>
+  <si>
+    <t>AGB_081</t>
+  </si>
+  <si>
+    <t>AGB_082</t>
+  </si>
+  <si>
+    <t>AGB_083</t>
+  </si>
+  <si>
+    <t>AGB_084</t>
+  </si>
+  <si>
+    <t>AGB_085</t>
+  </si>
+  <si>
+    <t>AGB_086</t>
+  </si>
+  <si>
+    <t>AGB_087</t>
+  </si>
+  <si>
+    <t>AGB_088</t>
+  </si>
+  <si>
+    <t>AGB_089</t>
+  </si>
+  <si>
+    <t>AGB_090</t>
+  </si>
+  <si>
+    <t>AGB_091</t>
+  </si>
+  <si>
+    <t>AGB_092</t>
+  </si>
+  <si>
+    <t>AGB_093</t>
+  </si>
+  <si>
+    <t>AGB_094</t>
+  </si>
+  <si>
+    <t>AGB_095</t>
+  </si>
+  <si>
+    <t>AGB_096</t>
+  </si>
+  <si>
+    <t>AGB_097</t>
+  </si>
+  <si>
+    <t>AGB_098</t>
+  </si>
+  <si>
+    <t>AGB_099</t>
+  </si>
+  <si>
+    <t>AGB_100</t>
+  </si>
+  <si>
+    <t>AGB_101</t>
+  </si>
+  <si>
+    <t>AGB_102</t>
+  </si>
+  <si>
+    <t>AGB_103</t>
+  </si>
+  <si>
+    <t>AGB_104</t>
+  </si>
+  <si>
+    <t>AGB_105</t>
+  </si>
+  <si>
+    <t>AGB_106</t>
+  </si>
+  <si>
+    <t>AGB_107</t>
+  </si>
+  <si>
+    <t>AGB_108</t>
+  </si>
+  <si>
+    <t>AGB_109</t>
+  </si>
+  <si>
+    <t>AGB_110</t>
+  </si>
+  <si>
+    <t>AGB_111</t>
+  </si>
+  <si>
+    <t>AGB_112</t>
+  </si>
+  <si>
+    <t>AGB_113</t>
+  </si>
+  <si>
+    <t>AGB_114</t>
+  </si>
+  <si>
+    <t>AGB_115</t>
+  </si>
+  <si>
+    <t>AGB_116</t>
+  </si>
+  <si>
+    <t>AGB_117</t>
+  </si>
+  <si>
+    <t>AGB_118</t>
+  </si>
+  <si>
+    <t>AGB_119</t>
+  </si>
+  <si>
+    <t>AGB_120</t>
+  </si>
+  <si>
+    <t>AGB_121</t>
+  </si>
+  <si>
+    <t>AGB_122</t>
+  </si>
+  <si>
+    <t>AGB_123</t>
+  </si>
+  <si>
+    <t>AGB_124</t>
+  </si>
+  <si>
+    <t>AGB_125</t>
+  </si>
+  <si>
+    <t>AGB_126</t>
+  </si>
+  <si>
+    <t>AGB_127</t>
+  </si>
+  <si>
+    <t>AGB_128</t>
+  </si>
+  <si>
+    <t>AGB_129</t>
+  </si>
+  <si>
+    <t>AGB_130</t>
+  </si>
+  <si>
+    <t>AGB_131</t>
+  </si>
+  <si>
+    <t>AGB_132</t>
+  </si>
+  <si>
+    <t>AGB_133</t>
+  </si>
+  <si>
+    <t>AGB_134</t>
+  </si>
+  <si>
+    <t>AGB_135</t>
+  </si>
+  <si>
+    <t>AGB_136</t>
+  </si>
+  <si>
+    <t>AGB_137</t>
+  </si>
+  <si>
+    <t>AGB_138</t>
+  </si>
+  <si>
+    <t>AGB_139</t>
+  </si>
+  <si>
+    <t>AGB_140</t>
+  </si>
+  <si>
+    <t>AGB_141</t>
+  </si>
+  <si>
+    <t>AGB_142</t>
+  </si>
+  <si>
+    <t>AGB_143</t>
+  </si>
+  <si>
+    <t>AGB_144</t>
+  </si>
+  <si>
+    <t>AGB_145</t>
+  </si>
+  <si>
+    <t>AGB_146</t>
+  </si>
+  <si>
+    <t>AGB_147</t>
+  </si>
+  <si>
+    <t>AGB_148</t>
+  </si>
+  <si>
+    <t>AGB_149</t>
+  </si>
+  <si>
+    <t>AGB_150</t>
+  </si>
+  <si>
+    <t>AGB_151</t>
+  </si>
+  <si>
+    <t>AGB_152</t>
+  </si>
+  <si>
+    <t>AGB_153</t>
+  </si>
+  <si>
+    <t>AGB_154</t>
+  </si>
+  <si>
+    <t>AGB_155</t>
+  </si>
+  <si>
+    <t>AGB_156</t>
+  </si>
+  <si>
+    <t>AGB_157</t>
+  </si>
+  <si>
+    <t>AGB_158</t>
+  </si>
+  <si>
+    <t>AGB_159</t>
+  </si>
+  <si>
+    <t>AGB_160</t>
+  </si>
+  <si>
+    <t>AGB_161</t>
+  </si>
+  <si>
+    <t>AGB_162</t>
+  </si>
+  <si>
+    <t>AGB_163</t>
+  </si>
+  <si>
+    <t>AGB_164</t>
+  </si>
+  <si>
+    <t>AGB_165</t>
+  </si>
+  <si>
+    <t>AGB_166</t>
+  </si>
+  <si>
+    <t>AGB_167</t>
+  </si>
+  <si>
+    <t>AGB_168</t>
+  </si>
+  <si>
+    <t>AGB_169</t>
+  </si>
+  <si>
+    <t>AGB_170</t>
+  </si>
+  <si>
+    <t>AGB_171</t>
+  </si>
+  <si>
+    <t>AGB_172</t>
+  </si>
+  <si>
+    <t>AGB_173</t>
+  </si>
+  <si>
+    <t>AGB_174</t>
+  </si>
+  <si>
+    <t>AGB_175</t>
+  </si>
+  <si>
+    <t>AGB_176</t>
+  </si>
+  <si>
+    <t>AGB_177</t>
+  </si>
+  <si>
     <t>As a wife, if your husband is cheating on you, it is YOUR OWN DECISION to make whether to continue with him or leave. If you decide to stay, let it be by YOUR OWN decision. If you value your mental health, your physical health your emotional health &amp; decide to leave, please do.</t>
   </si>
   <si>
@@ -548,13 +1088,547 @@
   </si>
   <si>
     <t>God please hide me from men that glorify cheating</t>
+  </si>
+  <si>
+    <t>https://x.com/efikedimbakara/status/1556954104173395971</t>
+  </si>
+  <si>
+    <t>https://x.com/Mareee_____/status/1556934959809560576</t>
+  </si>
+  <si>
+    <t>https://x.com/adesolahannah5/status/1556943773124403200</t>
+  </si>
+  <si>
+    <t>https://x.com/simply_abimbola/status/1557152982709460993</t>
+  </si>
+  <si>
+    <t>https://x.com/Verci_/status/1556794576274350081</t>
+  </si>
+  <si>
+    <t>https://x.com/chiomanatasha/status/1556765634611986432</t>
+  </si>
+  <si>
+    <t>https://x.com/TUNDEBANKOLE/status/1556871537344630784</t>
+  </si>
+  <si>
+    <t>https://x.com/AndrewMilton101/status/1556877948044693504</t>
+  </si>
+  <si>
+    <t>https://x.com/ohamadike_x/status/1557234422813966337</t>
+  </si>
+  <si>
+    <t>https://x.com/supreme03_12/status/1556882127135842305</t>
+  </si>
+  <si>
+    <t>https://x.com/Godcatalyst/status/1557116412514140167</t>
+  </si>
+  <si>
+    <t>https://x.com/GoodieSteffy/status/1556994286138413057</t>
+  </si>
+  <si>
+    <t>https://x.com/bridgetfidelis1/status/1557013300621312000</t>
+  </si>
+  <si>
+    <t>https://x.com/faddybaby2012/status/1557002871786315777</t>
+  </si>
+  <si>
+    <t>https://x.com/GiftUzor3/status/1556878750670901251</t>
+  </si>
+  <si>
+    <t>https://x.com/SAcholonu/status/1557046905393250307</t>
+  </si>
+  <si>
+    <t>https://x.com/ossaihillary1/status/1556977064128962561</t>
+  </si>
+  <si>
+    <t>https://x.com/WealthyBraine/status/1556757453840195586</t>
+  </si>
+  <si>
+    <t>https://x.com/GTproduction71/status/1556918552665489408</t>
+  </si>
+  <si>
+    <t>https://x.com/Juvangel1/status/1556768606289108992</t>
+  </si>
+  <si>
+    <t>https://x.com/Abu_y4all/status/1556788032187076611</t>
+  </si>
+  <si>
+    <t>https://x.com/ogahmonday6/status/1557072239585103873</t>
+  </si>
+  <si>
+    <t>https://x.com/SDSalawu/status/1556953484448104449</t>
+  </si>
+  <si>
+    <t>https://x.com/RoyalDheekor_/status/1556866142748250113</t>
+  </si>
+  <si>
+    <t>https://x.com/omarh_jay/status/1556936628580618240</t>
+  </si>
+  <si>
+    <t>https://x.com/simply_abimbola/status/1557155219393417222</t>
+  </si>
+  <si>
+    <t>https://x.com/TrustEderhi/status/1556941388947881991</t>
+  </si>
+  <si>
+    <t>https://x.com/OgeDichiVic/status/1556742750913150976</t>
+  </si>
+  <si>
+    <t>https://x.com/ekenekingsleys/status/1556936983066415104</t>
+  </si>
+  <si>
+    <t>https://x.com/mz_imaima/status/1556922003306725382</t>
+  </si>
+  <si>
+    <t>https://x.com/TeerachCraft/status/1556905606430314502</t>
+  </si>
+  <si>
+    <t>https://x.com/FrostyIcy2/status/1556943675980144640</t>
+  </si>
+  <si>
+    <t>https://x.com/BlackDiamond_97/status/1579678966650408960</t>
+  </si>
+  <si>
+    <t>https://x.com/SealOfSaints/status/1556774336530350081</t>
+  </si>
+  <si>
+    <t>https://x.com/uncle__enes/status/1556918614875332608</t>
+  </si>
+  <si>
+    <t>https://x.com/AmanThelma/status/1556969511244468228</t>
+  </si>
+  <si>
+    <t>https://x.com/BayodeBlessing2/status/1556956395790106624</t>
+  </si>
+  <si>
+    <t>https://x.com/BoniM_Ray/status/1557009774595694593</t>
+  </si>
+  <si>
+    <t>https://x.com/El_sa0000/status/1556888575899230210</t>
+  </si>
+  <si>
+    <t>https://x.com/_NelsonNosa/status/1556743250119098368</t>
+  </si>
+  <si>
+    <t>https://x.com/TheRealGadfly/status/1556880338764324870</t>
+  </si>
+  <si>
+    <t>https://x.com/FechiJudith/status/1556867310257840128</t>
+  </si>
+  <si>
+    <t>https://x.com/paddyalexltd/status/1556954886440468480</t>
+  </si>
+  <si>
+    <t>https://x.com/Oscar1_Baron/status/1557012283615854592</t>
+  </si>
+  <si>
+    <t>https://x.com/alinsbrown28/status/1556873993680048128</t>
+  </si>
+  <si>
+    <t>https://x.com/Patrickuchenn14/status/1556868333403766785</t>
+  </si>
+  <si>
+    <t>https://x.com/OSISUPER99/status/1556885751891197952</t>
+  </si>
+  <si>
+    <t>https://x.com/DRE_IVY/status/1557264600642588672</t>
+  </si>
+  <si>
+    <t>https://x.com/Tosin78441698/status/1556919148055330817</t>
+  </si>
+  <si>
+    <t>https://x.com/Domina11125768/status/1557027282660872194</t>
+  </si>
+  <si>
+    <t>https://x.com/Divycuteness/status/1556941704401412098</t>
+  </si>
+  <si>
+    <t>https://x.com/Chicstation/status/1556804126465564675</t>
+  </si>
+  <si>
+    <t>https://x.com/udocheeeee/status/1556952026197725185</t>
+  </si>
+  <si>
+    <t>https://x.com/nuelyodi/status/1556765408086167559</t>
+  </si>
+  <si>
+    <t>https://x.com/AdebisiAdunmad/status/1556743338379862020</t>
+  </si>
+  <si>
+    <t>https://x.com/Mumbari2/status/1556880639164461056</t>
+  </si>
+  <si>
+    <t>https://x.com/UCHE_BAMBAM/status/1556744072412495872</t>
+  </si>
+  <si>
+    <t>https://x.com/omarr__55/status/1556830071574364160</t>
+  </si>
+  <si>
+    <t>https://x.com/JumokeOgunkola/status/1557062379569020928</t>
+  </si>
+  <si>
+    <t>https://x.com/Ae_Seer/status/1556750850214723587</t>
+  </si>
+  <si>
+    <t>https://x.com/AbiolaTunde11/status/1556998406123429890</t>
+  </si>
+  <si>
+    <t>https://x.com/RantiDaDzna/status/1556925780160135168</t>
+  </si>
+  <si>
+    <t>https://x.com/simply_abimbola/status/1557154190803312640</t>
+  </si>
+  <si>
+    <t>https://x.com/Asuzu01180610/status/1558158982816096257</t>
+  </si>
+  <si>
+    <t>https://x.com/simply_abimbola/status/1557153606381572096</t>
+  </si>
+  <si>
+    <t>https://x.com/uncle__enes/status/1556919248617889792</t>
+  </si>
+  <si>
+    <t>https://x.com/bumstyle31/status/1556759636300206086</t>
+  </si>
+  <si>
+    <t>https://x.com/kris_tianah1/status/1556914033059667968</t>
+  </si>
+  <si>
+    <t>https://x.com/CriticDoe1/status/1558526447781830658</t>
+  </si>
+  <si>
+    <t>https://x.com/efikedimbakara/status/1556958041282584576</t>
+  </si>
+  <si>
+    <t>https://x.com/just_kater/status/1557136342018056198</t>
+  </si>
+  <si>
+    <t>https://x.com/NsikanDarby/status/1556753819568144384</t>
+  </si>
+  <si>
+    <t>https://x.com/normalflora_/status/1557297581348327425</t>
+  </si>
+  <si>
+    <t>https://x.com/HE_UncleMo/status/1556897825308479488</t>
+  </si>
+  <si>
+    <t>https://x.com/Ajanivictor61/status/1556888618232315905</t>
+  </si>
+  <si>
+    <t>https://x.com/femi619/status/1556912552583593990</t>
+  </si>
+  <si>
+    <t>https://x.com/Ade_Fury/status/1556745497620135942</t>
+  </si>
+  <si>
+    <t>https://x.com/chukstorino/status/1557037207671738371</t>
+  </si>
+  <si>
+    <t>https://x.com/daveedtimi/status/1557102172864667648</t>
+  </si>
+  <si>
+    <t>https://x.com/bluprint7g/status/1556747801593249793</t>
+  </si>
+  <si>
+    <t>https://x.com/Mandie55980150/status/1556989055975448579</t>
+  </si>
+  <si>
+    <t>https://x.com/_MIGHTYKINGSLEY/status/1557061007788359680</t>
+  </si>
+  <si>
+    <t>https://x.com/finegirljb/status/1557021298425053184</t>
+  </si>
+  <si>
+    <t>https://x.com/stanfizzy/status/1556945676973608962</t>
+  </si>
+  <si>
+    <t>https://x.com/frostieees_/status/1556961125459165192</t>
+  </si>
+  <si>
+    <t>https://x.com/e_gmajor/status/1556835036296785921</t>
+  </si>
+  <si>
+    <t>https://x.com/Sonsofegedege/status/1556958986892677122</t>
+  </si>
+  <si>
+    <t>https://x.com/Fat2Fitklub/status/1556800933656510464</t>
+  </si>
+  <si>
+    <t>https://x.com/Miz_is_tim/status/1556978823727665156</t>
+  </si>
+  <si>
+    <t>https://x.com/SimpsonOjie/status/1556886872114270208</t>
+  </si>
+  <si>
+    <t>https://x.com/yosei_harlequin/status/1556910634775740416</t>
+  </si>
+  <si>
+    <t>https://x.com/D_POSSIBILITIX/status/1556892684526166016</t>
+  </si>
+  <si>
+    <t>https://x.com/Tonde_Shamu/status/1556836117542064129</t>
+  </si>
+  <si>
+    <t>https://x.com/Ritachinny2/status/1556961411238092801</t>
+  </si>
+  <si>
+    <t>https://x.com/Topsehtee/status/1556747712351158273</t>
+  </si>
+  <si>
+    <t>https://x.com/Mareee_____/status/1556935671431970816</t>
+  </si>
+  <si>
+    <t>https://x.com/IbekweEmmanue20/status/1556754010715181057</t>
+  </si>
+  <si>
+    <t>https://x.com/Vickiemee200/status/1556761413162524677</t>
+  </si>
+  <si>
+    <t>https://x.com/ChiamakaNwaJohn/status/1556928195340935170</t>
+  </si>
+  <si>
+    <t>https://x.com/HE_UncleMo/status/1556901735880351744</t>
+  </si>
+  <si>
+    <t>https://x.com/_agu_eze/status/1556910670251282432</t>
+  </si>
+  <si>
+    <t>https://x.com/Favywhyte/status/1557032764712669184</t>
+  </si>
+  <si>
+    <t>https://x.com/TheMemoirGhost/status/1556923576720281600</t>
+  </si>
+  <si>
+    <t>https://x.com/djgodson/status/1557121289948696576</t>
+  </si>
+  <si>
+    <t>https://x.com/Jo_4444real/status/1556975925631262720</t>
+  </si>
+  <si>
+    <t>https://x.com/TUNDEBANKOLE/status/1556870476290482180</t>
+  </si>
+  <si>
+    <t>https://x.com/PenTitan/status/1556755818950922240</t>
+  </si>
+  <si>
+    <t>https://x.com/ras_ogbu/status/1557076677448339457</t>
+  </si>
+  <si>
+    <t>https://x.com/Ucee_Dave/status/1556958497509703680</t>
+  </si>
+  <si>
+    <t>https://x.com/2Ekos/status/1557037264483586048</t>
+  </si>
+  <si>
+    <t>https://x.com/BPharmeno/status/1556782790745669632</t>
+  </si>
+  <si>
+    <t>https://x.com/Ladychelgift/status/1556940731071201280</t>
+  </si>
+  <si>
+    <t>https://x.com/DataneserConsu1/status/1556935288961880064</t>
+  </si>
+  <si>
+    <t>https://x.com/CassieChris3/status/1557021231899082752</t>
+  </si>
+  <si>
+    <t>https://x.com/Daninonify/status/1557077399996698624</t>
+  </si>
+  <si>
+    <t>https://x.com/figman_deezign/status/1557019797514330112</t>
+  </si>
+  <si>
+    <t>https://x.com/mac_phi/status/1557064628953354242</t>
+  </si>
+  <si>
+    <t>https://x.com/efikedimbakara/status/1557000365077323776</t>
+  </si>
+  <si>
+    <t>https://x.com/AinaKay1/status/1556995193689227265</t>
+  </si>
+  <si>
+    <t>https://x.com/Sir_Joe__/status/1556765287696982017</t>
+  </si>
+  <si>
+    <t>https://x.com/RowlandOkwong/status/1557188867723333639</t>
+  </si>
+  <si>
+    <t>https://x.com/sweetabbyjay/status/1556880736409604097</t>
+  </si>
+  <si>
+    <t>https://x.com/ChiamakaNwaJohn/status/1556926523789266945</t>
+  </si>
+  <si>
+    <t>https://x.com/paskahl_/status/1556938559080337408</t>
+  </si>
+  <si>
+    <t>https://x.com/BPharmeno/status/1556783419039907841</t>
+  </si>
+  <si>
+    <t>https://x.com/goodhoursx/status/1556939161243828226</t>
+  </si>
+  <si>
+    <t>https://x.com/BPharmeno/status/1556784981950734336</t>
+  </si>
+  <si>
+    <t>https://x.com/Ayerish2715/status/1556967167798788096</t>
+  </si>
+  <si>
+    <t>https://x.com/mosesajik/status/1556768037323378692</t>
+  </si>
+  <si>
+    <t>https://x.com/fairy_smiles/status/1557309108109426688</t>
+  </si>
+  <si>
+    <t>https://x.com/nasircush/status/1557012423277776898</t>
+  </si>
+  <si>
+    <t>https://x.com/ellyxmusic/status/1556826468461805568</t>
+  </si>
+  <si>
+    <t>https://x.com/Franklinoh/status/1556927893049167872</t>
+  </si>
+  <si>
+    <t>https://x.com/lagosAbujaGirl/status/1556908211697061888</t>
+  </si>
+  <si>
+    <t>https://x.com/Ogbeski/status/1556887322343473153</t>
+  </si>
+  <si>
+    <t>https://x.com/damrid_/status/1556883200936448000</t>
+  </si>
+  <si>
+    <t>https://x.com/Abdgofars/status/1556941935226519552</t>
+  </si>
+  <si>
+    <t>https://x.com/EricKAliya/status/1556909710653231105</t>
+  </si>
+  <si>
+    <t>https://x.com/shashupenz/status/1557041878494855170</t>
+  </si>
+  <si>
+    <t>https://x.com/Theagronomistt/status/1557026392746987520</t>
+  </si>
+  <si>
+    <t>https://x.com/CarolineTochi/status/1556829040690040834</t>
+  </si>
+  <si>
+    <t>https://x.com/Jay_1883/status/1556911566527905803</t>
+  </si>
+  <si>
+    <t>https://x.com/VictorOvon/status/1556758218239606787</t>
+  </si>
+  <si>
+    <t>https://x.com/XfromTok/status/1556965575087243272</t>
+  </si>
+  <si>
+    <t>https://x.com/amazingjoyfalz/status/1556774730736205825</t>
+  </si>
+  <si>
+    <t>https://x.com/TenQQGod/status/1556985808829259777</t>
+  </si>
+  <si>
+    <t>https://x.com/JenniferOpara1/status/1556904023181123584</t>
+  </si>
+  <si>
+    <t>https://x.com/Iamzeus4u/status/1557032390928769026</t>
+  </si>
+  <si>
+    <t>https://x.com/VickBlaze123/status/1556741043852386306</t>
+  </si>
+  <si>
+    <t>https://x.com/QueenMotherFeyi/status/1557065455839354882</t>
+  </si>
+  <si>
+    <t>https://x.com/WhizMatty/status/1556890077283995653</t>
+  </si>
+  <si>
+    <t>https://x.com/preshrich/status/1557040571843330049</t>
+  </si>
+  <si>
+    <t>https://x.com/Legit4_4/status/1556744622990311424</t>
+  </si>
+  <si>
+    <t>https://x.com/afolabiadedayo/status/1556999939238027264</t>
+  </si>
+  <si>
+    <t>https://x.com/legit_ovacomer/status/1556942587709325313</t>
+  </si>
+  <si>
+    <t>https://x.com/ejim_cyril/status/1557099795717701639</t>
+  </si>
+  <si>
+    <t>https://x.com/vera_nuel/status/1557465276689547266</t>
+  </si>
+  <si>
+    <t>https://x.com/McwylieWrites/status/1556882712711106560</t>
+  </si>
+  <si>
+    <t>https://x.com/vchi_30/status/1557100347834998788</t>
+  </si>
+  <si>
+    <t>https://x.com/MayorofMyHouse/status/1556947239741833216</t>
+  </si>
+  <si>
+    <t>https://x.com/Ms_Happie_Obus/status/1557060259402981379</t>
+  </si>
+  <si>
+    <t>https://x.com/MacFoso/status/1556851770357387264</t>
+  </si>
+  <si>
+    <t>https://x.com/IbibienVivian/status/1556951773788659713</t>
+  </si>
+  <si>
+    <t>https://x.com/NurseeHakeem/status/1556867217450536963</t>
+  </si>
+  <si>
+    <t>https://x.com/SLPvv1/status/1556884117446434817</t>
+  </si>
+  <si>
+    <t>https://x.com/RDSanders007/status/1556875520255705088</t>
+  </si>
+  <si>
+    <t>https://x.com/AbiolaBlaq/status/1556957344814227457</t>
+  </si>
+  <si>
+    <t>https://x.com/Foedosa1/status/1556871078294732800</t>
+  </si>
+  <si>
+    <t>https://x.com/BawiKehinde/status/1557040319555837952</t>
+  </si>
+  <si>
+    <t>https://x.com/Dmichi7/status/1556743246050693120</t>
+  </si>
+  <si>
+    <t>https://x.com/stanfizzy/status/1556948818393964544</t>
+  </si>
+  <si>
+    <t>https://x.com/FEghreriniovo/status/1556951064053780483</t>
+  </si>
+  <si>
+    <t>https://x.com/prettyposh5/status/1556744045128548352</t>
+  </si>
+  <si>
+    <t>https://x.com/Ajoke_2020/status/1556940633931145216</t>
+  </si>
+  <si>
+    <t>https://x.com/Be_nita1/status/1556960078699417601</t>
+  </si>
+  <si>
+    <t>https://x.com/iamkhaleefa1/status/1557236595509583872</t>
+  </si>
+  <si>
+    <t>https://x.com/thatPreciousg/status/1557313667477168128</t>
+  </si>
+  <si>
+    <t>https://x.com/jon_d_doe/status/1556739908810817536</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -569,6 +1643,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -603,16 +1684,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -905,900 +1992,2858 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A178"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>212</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
+        <v>39</v>
+      </c>
+      <c r="B37" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
+        <v>217</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>218</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
+        <v>42</v>
+      </c>
+      <c r="B40" t="s">
+        <v>219</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
+        <v>43</v>
+      </c>
+      <c r="B41" t="s">
+        <v>220</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>221</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
+        <v>45</v>
+      </c>
+      <c r="B43" t="s">
+        <v>222</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>223</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s">
+        <v>224</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>225</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
+        <v>49</v>
+      </c>
+      <c r="B47" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
+        <v>50</v>
+      </c>
+      <c r="B48" t="s">
+        <v>227</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
+        <v>51</v>
+      </c>
+      <c r="B49" t="s">
+        <v>228</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
+        <v>52</v>
+      </c>
+      <c r="B50" t="s">
+        <v>229</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
+        <v>53</v>
+      </c>
+      <c r="B51" t="s">
+        <v>230</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
+        <v>54</v>
+      </c>
+      <c r="B52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
+        <v>55</v>
+      </c>
+      <c r="B53" t="s">
+        <v>232</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
+        <v>56</v>
+      </c>
+      <c r="B54" t="s">
+        <v>233</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
+        <v>57</v>
+      </c>
+      <c r="B55" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
+        <v>58</v>
+      </c>
+      <c r="B56" t="s">
+        <v>235</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
+        <v>59</v>
+      </c>
+      <c r="B57" t="s">
+        <v>236</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
+        <v>60</v>
+      </c>
+      <c r="B58" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
+        <v>61</v>
+      </c>
+      <c r="B59" t="s">
+        <v>238</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
+        <v>62</v>
+      </c>
+      <c r="B60" t="s">
+        <v>239</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
+        <v>63</v>
+      </c>
+      <c r="B61" t="s">
+        <v>240</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
+        <v>64</v>
+      </c>
+      <c r="B62" t="s">
+        <v>241</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
+        <v>65</v>
+      </c>
+      <c r="B63" t="s">
+        <v>242</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
+        <v>66</v>
+      </c>
+      <c r="B64" t="s">
+        <v>243</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
+        <v>67</v>
+      </c>
+      <c r="B65" t="s">
+        <v>244</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
+        <v>68</v>
+      </c>
+      <c r="B66" t="s">
+        <v>245</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
+        <v>69</v>
+      </c>
+      <c r="B67" t="s">
+        <v>246</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
+        <v>70</v>
+      </c>
+      <c r="B68" t="s">
+        <v>247</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
+        <v>71</v>
+      </c>
+      <c r="B69" t="s">
+        <v>248</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
+        <v>72</v>
+      </c>
+      <c r="B70" t="s">
+        <v>249</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
+        <v>73</v>
+      </c>
+      <c r="B71" t="s">
+        <v>250</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
+        <v>74</v>
+      </c>
+      <c r="B72" t="s">
+        <v>251</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
+        <v>75</v>
+      </c>
+      <c r="B73" t="s">
+        <v>252</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
+        <v>76</v>
+      </c>
+      <c r="B74" t="s">
+        <v>253</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
+        <v>77</v>
+      </c>
+      <c r="B75" t="s">
+        <v>254</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
+        <v>78</v>
+      </c>
+      <c r="B76" t="s">
+        <v>255</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
+        <v>79</v>
+      </c>
+      <c r="B77" t="s">
+        <v>256</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
+        <v>80</v>
+      </c>
+      <c r="B78" t="s">
+        <v>257</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
+        <v>81</v>
+      </c>
+      <c r="B79" t="s">
+        <v>258</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
+        <v>82</v>
+      </c>
+      <c r="B80" t="s">
+        <v>259</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
+        <v>83</v>
+      </c>
+      <c r="B81" t="s">
+        <v>260</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
+        <v>84</v>
+      </c>
+      <c r="B82" t="s">
+        <v>261</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
+        <v>85</v>
+      </c>
+      <c r="B83" t="s">
+        <v>262</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
+        <v>86</v>
+      </c>
+      <c r="B84" t="s">
+        <v>263</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
+        <v>87</v>
+      </c>
+      <c r="B85" t="s">
+        <v>264</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
+        <v>88</v>
+      </c>
+      <c r="B86" t="s">
+        <v>265</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
+        <v>89</v>
+      </c>
+      <c r="B87" t="s">
+        <v>266</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
+        <v>90</v>
+      </c>
+      <c r="B88" t="s">
+        <v>267</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
+        <v>91</v>
+      </c>
+      <c r="B89" t="s">
+        <v>268</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
+        <v>92</v>
+      </c>
+      <c r="B90" t="s">
+        <v>269</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
+        <v>93</v>
+      </c>
+      <c r="B91" t="s">
+        <v>270</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
+        <v>94</v>
+      </c>
+      <c r="B92" t="s">
+        <v>271</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
+        <v>95</v>
+      </c>
+      <c r="B93" t="s">
+        <v>272</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
+        <v>96</v>
+      </c>
+      <c r="B94" t="s">
+        <v>273</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
+        <v>97</v>
+      </c>
+      <c r="B95" t="s">
+        <v>274</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
+        <v>98</v>
+      </c>
+      <c r="B96" t="s">
+        <v>275</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
+        <v>99</v>
+      </c>
+      <c r="B97" t="s">
+        <v>276</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
+        <v>100</v>
+      </c>
+      <c r="B98" t="s">
+        <v>277</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
+        <v>101</v>
+      </c>
+      <c r="B99" t="s">
+        <v>278</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
+        <v>102</v>
+      </c>
+      <c r="B100" t="s">
+        <v>279</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
+        <v>103</v>
+      </c>
+      <c r="B101" t="s">
+        <v>280</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
+        <v>104</v>
+      </c>
+      <c r="B102" t="s">
+        <v>281</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
+        <v>105</v>
+      </c>
+      <c r="B103" t="s">
+        <v>282</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
+        <v>106</v>
+      </c>
+      <c r="B104" t="s">
+        <v>283</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
+        <v>107</v>
+      </c>
+      <c r="B105" t="s">
+        <v>284</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
+        <v>108</v>
+      </c>
+      <c r="B106" t="s">
+        <v>285</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
+        <v>109</v>
+      </c>
+      <c r="B107" t="s">
+        <v>286</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
+        <v>110</v>
+      </c>
+      <c r="B108" t="s">
+        <v>287</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
+        <v>111</v>
+      </c>
+      <c r="B109" t="s">
+        <v>288</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
+        <v>112</v>
+      </c>
+      <c r="B110" t="s">
+        <v>289</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
+        <v>113</v>
+      </c>
+      <c r="B111" t="s">
+        <v>290</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
+        <v>114</v>
+      </c>
+      <c r="B112" t="s">
+        <v>291</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
+        <v>115</v>
+      </c>
+      <c r="B113" t="s">
+        <v>292</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
+        <v>116</v>
+      </c>
+      <c r="B114" t="s">
+        <v>293</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
+        <v>117</v>
+      </c>
+      <c r="B115" t="s">
+        <v>294</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
+        <v>118</v>
+      </c>
+      <c r="B116" t="s">
+        <v>295</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
+        <v>119</v>
+      </c>
+      <c r="B117" t="s">
+        <v>296</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
+        <v>120</v>
+      </c>
+      <c r="B118" t="s">
+        <v>297</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
+        <v>121</v>
+      </c>
+      <c r="B119" t="s">
+        <v>298</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
+        <v>122</v>
+      </c>
+      <c r="B120" t="s">
+        <v>299</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
+        <v>123</v>
+      </c>
+      <c r="B121" t="s">
+        <v>300</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
+        <v>124</v>
+      </c>
+      <c r="B122" t="s">
+        <v>301</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
+        <v>125</v>
+      </c>
+      <c r="B123" t="s">
+        <v>302</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
+        <v>126</v>
+      </c>
+      <c r="B124" t="s">
+        <v>303</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
+        <v>127</v>
+      </c>
+      <c r="B125" t="s">
+        <v>304</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
+        <v>128</v>
+      </c>
+      <c r="B126" t="s">
+        <v>305</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
+        <v>129</v>
+      </c>
+      <c r="B127" t="s">
+        <v>306</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
+        <v>130</v>
+      </c>
+      <c r="B128" t="s">
+        <v>307</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
+        <v>131</v>
+      </c>
+      <c r="B129" t="s">
+        <v>308</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
+        <v>132</v>
+      </c>
+      <c r="B130" t="s">
+        <v>309</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
+        <v>133</v>
+      </c>
+      <c r="B131" t="s">
+        <v>310</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
+        <v>134</v>
+      </c>
+      <c r="B132" t="s">
+        <v>311</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
+        <v>135</v>
+      </c>
+      <c r="B133" t="s">
+        <v>312</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
+        <v>136</v>
+      </c>
+      <c r="B134" t="s">
+        <v>313</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
+        <v>137</v>
+      </c>
+      <c r="B135" t="s">
+        <v>314</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
+        <v>138</v>
+      </c>
+      <c r="B136" t="s">
+        <v>315</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
+        <v>139</v>
+      </c>
+      <c r="B137" t="s">
+        <v>316</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
+        <v>140</v>
+      </c>
+      <c r="B138" t="s">
+        <v>317</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
+        <v>141</v>
+      </c>
+      <c r="B139" t="s">
+        <v>318</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
+        <v>142</v>
+      </c>
+      <c r="B140" t="s">
+        <v>319</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
+        <v>143</v>
+      </c>
+      <c r="B141" t="s">
+        <v>320</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
+        <v>144</v>
+      </c>
+      <c r="B142" t="s">
+        <v>321</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
+        <v>145</v>
+      </c>
+      <c r="B143" t="s">
+        <v>322</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
+        <v>146</v>
+      </c>
+      <c r="B144" t="s">
+        <v>323</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
+        <v>147</v>
+      </c>
+      <c r="B145" t="s">
+        <v>324</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
+        <v>148</v>
+      </c>
+      <c r="B146" t="s">
+        <v>325</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
+        <v>149</v>
+      </c>
+      <c r="B147" t="s">
+        <v>326</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
+        <v>150</v>
+      </c>
+      <c r="B148" t="s">
+        <v>327</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
+        <v>151</v>
+      </c>
+      <c r="B149" t="s">
+        <v>328</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
+        <v>152</v>
+      </c>
+      <c r="B150" t="s">
+        <v>329</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
+        <v>153</v>
+      </c>
+      <c r="B151" t="s">
+        <v>330</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
+        <v>154</v>
+      </c>
+      <c r="B152" t="s">
+        <v>331</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
+        <v>155</v>
+      </c>
+      <c r="B153" t="s">
+        <v>332</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
+        <v>156</v>
+      </c>
+      <c r="B154" t="s">
+        <v>333</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
+        <v>157</v>
+      </c>
+      <c r="B155" t="s">
+        <v>334</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1">
+        <v>158</v>
+      </c>
+      <c r="B156" t="s">
+        <v>335</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
+        <v>159</v>
+      </c>
+      <c r="B157" t="s">
+        <v>336</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
+        <v>160</v>
+      </c>
+      <c r="B158" t="s">
+        <v>337</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
+        <v>161</v>
+      </c>
+      <c r="B159" t="s">
+        <v>338</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
+        <v>162</v>
+      </c>
+      <c r="B160" t="s">
+        <v>339</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
+        <v>163</v>
+      </c>
+      <c r="B161" t="s">
+        <v>340</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
+        <v>164</v>
+      </c>
+      <c r="B162" t="s">
+        <v>341</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
+        <v>165</v>
+      </c>
+      <c r="B163" t="s">
+        <v>342</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
+        <v>166</v>
+      </c>
+      <c r="B164" t="s">
+        <v>343</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
+        <v>167</v>
+      </c>
+      <c r="B165" t="s">
+        <v>344</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
+        <v>168</v>
+      </c>
+      <c r="B166" t="s">
+        <v>345</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
+        <v>169</v>
+      </c>
+      <c r="B167" t="s">
+        <v>346</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
+        <v>170</v>
+      </c>
+      <c r="B168" t="s">
+        <v>347</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
+        <v>171</v>
+      </c>
+      <c r="B169" t="s">
+        <v>348</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
+        <v>172</v>
+      </c>
+      <c r="B170" t="s">
+        <v>349</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
+        <v>173</v>
+      </c>
+      <c r="B171" t="s">
+        <v>350</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
+        <v>174</v>
+      </c>
+      <c r="B172" t="s">
+        <v>351</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
+        <v>175</v>
+      </c>
+      <c r="B173" t="s">
+        <v>352</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
+        <v>176</v>
+      </c>
+      <c r="B174" t="s">
+        <v>353</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
+        <v>177</v>
+      </c>
+      <c r="B175" t="s">
+        <v>354</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
+        <v>178</v>
+      </c>
+      <c r="B176" t="s">
+        <v>355</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
+        <v>179</v>
+      </c>
+      <c r="B177" t="s">
+        <v>356</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>177</v>
+        <v>180</v>
+      </c>
+      <c r="B178" t="s">
+        <v>357</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>535</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="D2" r:id="rId2"/>
+    <hyperlink ref="C3" r:id="rId3"/>
+    <hyperlink ref="D3" r:id="rId4"/>
+    <hyperlink ref="C4" r:id="rId5"/>
+    <hyperlink ref="D4" r:id="rId6"/>
+    <hyperlink ref="C5" r:id="rId7"/>
+    <hyperlink ref="D5" r:id="rId8"/>
+    <hyperlink ref="C6" r:id="rId9"/>
+    <hyperlink ref="D6" r:id="rId10"/>
+    <hyperlink ref="C7" r:id="rId11"/>
+    <hyperlink ref="D7" r:id="rId12"/>
+    <hyperlink ref="C8" r:id="rId13"/>
+    <hyperlink ref="D8" r:id="rId14"/>
+    <hyperlink ref="C9" r:id="rId15"/>
+    <hyperlink ref="D9" r:id="rId16"/>
+    <hyperlink ref="C10" r:id="rId17"/>
+    <hyperlink ref="D10" r:id="rId18"/>
+    <hyperlink ref="C11" r:id="rId19"/>
+    <hyperlink ref="D11" r:id="rId20"/>
+    <hyperlink ref="C12" r:id="rId21"/>
+    <hyperlink ref="D12" r:id="rId22"/>
+    <hyperlink ref="C13" r:id="rId23"/>
+    <hyperlink ref="D13" r:id="rId24"/>
+    <hyperlink ref="C14" r:id="rId25"/>
+    <hyperlink ref="D14" r:id="rId26"/>
+    <hyperlink ref="C15" r:id="rId27"/>
+    <hyperlink ref="D15" r:id="rId28"/>
+    <hyperlink ref="C16" r:id="rId29"/>
+    <hyperlink ref="D16" r:id="rId30"/>
+    <hyperlink ref="C17" r:id="rId31"/>
+    <hyperlink ref="D17" r:id="rId32"/>
+    <hyperlink ref="C18" r:id="rId33"/>
+    <hyperlink ref="D18" r:id="rId34"/>
+    <hyperlink ref="C19" r:id="rId35"/>
+    <hyperlink ref="D19" r:id="rId36"/>
+    <hyperlink ref="C20" r:id="rId37"/>
+    <hyperlink ref="D20" r:id="rId38"/>
+    <hyperlink ref="C21" r:id="rId39"/>
+    <hyperlink ref="D21" r:id="rId40"/>
+    <hyperlink ref="C22" r:id="rId41"/>
+    <hyperlink ref="D22" r:id="rId42"/>
+    <hyperlink ref="C23" r:id="rId43"/>
+    <hyperlink ref="D23" r:id="rId44"/>
+    <hyperlink ref="C24" r:id="rId45"/>
+    <hyperlink ref="D24" r:id="rId46"/>
+    <hyperlink ref="C25" r:id="rId47"/>
+    <hyperlink ref="D25" r:id="rId48"/>
+    <hyperlink ref="C26" r:id="rId49"/>
+    <hyperlink ref="D26" r:id="rId50"/>
+    <hyperlink ref="C27" r:id="rId51"/>
+    <hyperlink ref="D27" r:id="rId52"/>
+    <hyperlink ref="C28" r:id="rId53"/>
+    <hyperlink ref="D28" r:id="rId54"/>
+    <hyperlink ref="C29" r:id="rId55"/>
+    <hyperlink ref="D29" r:id="rId56"/>
+    <hyperlink ref="C30" r:id="rId57"/>
+    <hyperlink ref="D30" r:id="rId58"/>
+    <hyperlink ref="C31" r:id="rId59"/>
+    <hyperlink ref="D31" r:id="rId60"/>
+    <hyperlink ref="C32" r:id="rId61"/>
+    <hyperlink ref="D32" r:id="rId62"/>
+    <hyperlink ref="C33" r:id="rId63"/>
+    <hyperlink ref="D33" r:id="rId64"/>
+    <hyperlink ref="C34" r:id="rId65"/>
+    <hyperlink ref="D34" r:id="rId66"/>
+    <hyperlink ref="C35" r:id="rId67"/>
+    <hyperlink ref="D35" r:id="rId68"/>
+    <hyperlink ref="C36" r:id="rId69"/>
+    <hyperlink ref="D36" r:id="rId70"/>
+    <hyperlink ref="C37" r:id="rId71"/>
+    <hyperlink ref="D37" r:id="rId72"/>
+    <hyperlink ref="C38" r:id="rId73"/>
+    <hyperlink ref="D38" r:id="rId74"/>
+    <hyperlink ref="C39" r:id="rId75"/>
+    <hyperlink ref="D39" r:id="rId76"/>
+    <hyperlink ref="C40" r:id="rId77"/>
+    <hyperlink ref="D40" r:id="rId78"/>
+    <hyperlink ref="C41" r:id="rId79"/>
+    <hyperlink ref="D41" r:id="rId80"/>
+    <hyperlink ref="C42" r:id="rId81"/>
+    <hyperlink ref="D42" r:id="rId82"/>
+    <hyperlink ref="C43" r:id="rId83"/>
+    <hyperlink ref="D43" r:id="rId84"/>
+    <hyperlink ref="C44" r:id="rId85"/>
+    <hyperlink ref="D44" r:id="rId86"/>
+    <hyperlink ref="C45" r:id="rId87"/>
+    <hyperlink ref="D45" r:id="rId88"/>
+    <hyperlink ref="C46" r:id="rId89"/>
+    <hyperlink ref="D46" r:id="rId90"/>
+    <hyperlink ref="C47" r:id="rId91"/>
+    <hyperlink ref="D47" r:id="rId92"/>
+    <hyperlink ref="C48" r:id="rId93"/>
+    <hyperlink ref="D48" r:id="rId94"/>
+    <hyperlink ref="C49" r:id="rId95"/>
+    <hyperlink ref="D49" r:id="rId96"/>
+    <hyperlink ref="C50" r:id="rId97"/>
+    <hyperlink ref="D50" r:id="rId98"/>
+    <hyperlink ref="C51" r:id="rId99"/>
+    <hyperlink ref="D51" r:id="rId100"/>
+    <hyperlink ref="C52" r:id="rId101"/>
+    <hyperlink ref="D52" r:id="rId102"/>
+    <hyperlink ref="C53" r:id="rId103"/>
+    <hyperlink ref="D53" r:id="rId104"/>
+    <hyperlink ref="C54" r:id="rId105"/>
+    <hyperlink ref="D54" r:id="rId106"/>
+    <hyperlink ref="C55" r:id="rId107"/>
+    <hyperlink ref="D55" r:id="rId108"/>
+    <hyperlink ref="C56" r:id="rId109"/>
+    <hyperlink ref="D56" r:id="rId110"/>
+    <hyperlink ref="C57" r:id="rId111"/>
+    <hyperlink ref="D57" r:id="rId112"/>
+    <hyperlink ref="C58" r:id="rId113"/>
+    <hyperlink ref="D58" r:id="rId114"/>
+    <hyperlink ref="C59" r:id="rId115"/>
+    <hyperlink ref="D59" r:id="rId116"/>
+    <hyperlink ref="C60" r:id="rId117"/>
+    <hyperlink ref="D60" r:id="rId118"/>
+    <hyperlink ref="C61" r:id="rId119"/>
+    <hyperlink ref="D61" r:id="rId120"/>
+    <hyperlink ref="C62" r:id="rId121"/>
+    <hyperlink ref="D62" r:id="rId122"/>
+    <hyperlink ref="C63" r:id="rId123"/>
+    <hyperlink ref="D63" r:id="rId124"/>
+    <hyperlink ref="C64" r:id="rId125"/>
+    <hyperlink ref="D64" r:id="rId126"/>
+    <hyperlink ref="C65" r:id="rId127"/>
+    <hyperlink ref="D65" r:id="rId128"/>
+    <hyperlink ref="C66" r:id="rId129"/>
+    <hyperlink ref="D66" r:id="rId130"/>
+    <hyperlink ref="C67" r:id="rId131"/>
+    <hyperlink ref="D67" r:id="rId132"/>
+    <hyperlink ref="C68" r:id="rId133"/>
+    <hyperlink ref="D68" r:id="rId134"/>
+    <hyperlink ref="C69" r:id="rId135"/>
+    <hyperlink ref="D69" r:id="rId136"/>
+    <hyperlink ref="C70" r:id="rId137"/>
+    <hyperlink ref="D70" r:id="rId138"/>
+    <hyperlink ref="C71" r:id="rId139"/>
+    <hyperlink ref="D71" r:id="rId140"/>
+    <hyperlink ref="C72" r:id="rId141"/>
+    <hyperlink ref="D72" r:id="rId142"/>
+    <hyperlink ref="C73" r:id="rId143"/>
+    <hyperlink ref="D73" r:id="rId144"/>
+    <hyperlink ref="C74" r:id="rId145"/>
+    <hyperlink ref="D74" r:id="rId146"/>
+    <hyperlink ref="C75" r:id="rId147"/>
+    <hyperlink ref="D75" r:id="rId148"/>
+    <hyperlink ref="C76" r:id="rId149"/>
+    <hyperlink ref="D76" r:id="rId150"/>
+    <hyperlink ref="C77" r:id="rId151"/>
+    <hyperlink ref="D77" r:id="rId152"/>
+    <hyperlink ref="C78" r:id="rId153"/>
+    <hyperlink ref="D78" r:id="rId154"/>
+    <hyperlink ref="C79" r:id="rId155"/>
+    <hyperlink ref="D79" r:id="rId156"/>
+    <hyperlink ref="C80" r:id="rId157"/>
+    <hyperlink ref="D80" r:id="rId158"/>
+    <hyperlink ref="C81" r:id="rId159"/>
+    <hyperlink ref="D81" r:id="rId160"/>
+    <hyperlink ref="C82" r:id="rId161"/>
+    <hyperlink ref="D82" r:id="rId162"/>
+    <hyperlink ref="C83" r:id="rId163"/>
+    <hyperlink ref="D83" r:id="rId164"/>
+    <hyperlink ref="C84" r:id="rId165"/>
+    <hyperlink ref="D84" r:id="rId166"/>
+    <hyperlink ref="C85" r:id="rId167"/>
+    <hyperlink ref="D85" r:id="rId168"/>
+    <hyperlink ref="C86" r:id="rId169"/>
+    <hyperlink ref="D86" r:id="rId170"/>
+    <hyperlink ref="C87" r:id="rId171"/>
+    <hyperlink ref="D87" r:id="rId172"/>
+    <hyperlink ref="C88" r:id="rId173"/>
+    <hyperlink ref="D88" r:id="rId174"/>
+    <hyperlink ref="C89" r:id="rId175"/>
+    <hyperlink ref="D89" r:id="rId176"/>
+    <hyperlink ref="C90" r:id="rId177"/>
+    <hyperlink ref="D90" r:id="rId178"/>
+    <hyperlink ref="C91" r:id="rId179"/>
+    <hyperlink ref="D91" r:id="rId180"/>
+    <hyperlink ref="C92" r:id="rId181"/>
+    <hyperlink ref="D92" r:id="rId182"/>
+    <hyperlink ref="C93" r:id="rId183"/>
+    <hyperlink ref="D93" r:id="rId184"/>
+    <hyperlink ref="C94" r:id="rId185"/>
+    <hyperlink ref="D94" r:id="rId186"/>
+    <hyperlink ref="C95" r:id="rId187"/>
+    <hyperlink ref="D95" r:id="rId188"/>
+    <hyperlink ref="C96" r:id="rId189"/>
+    <hyperlink ref="D96" r:id="rId190"/>
+    <hyperlink ref="C97" r:id="rId191"/>
+    <hyperlink ref="D97" r:id="rId192"/>
+    <hyperlink ref="C98" r:id="rId193"/>
+    <hyperlink ref="D98" r:id="rId194"/>
+    <hyperlink ref="C99" r:id="rId195"/>
+    <hyperlink ref="D99" r:id="rId196"/>
+    <hyperlink ref="C100" r:id="rId197"/>
+    <hyperlink ref="D100" r:id="rId198"/>
+    <hyperlink ref="C101" r:id="rId199"/>
+    <hyperlink ref="D101" r:id="rId200"/>
+    <hyperlink ref="C102" r:id="rId201"/>
+    <hyperlink ref="D102" r:id="rId202"/>
+    <hyperlink ref="C103" r:id="rId203"/>
+    <hyperlink ref="D103" r:id="rId204"/>
+    <hyperlink ref="C104" r:id="rId205"/>
+    <hyperlink ref="D104" r:id="rId206"/>
+    <hyperlink ref="C105" r:id="rId207"/>
+    <hyperlink ref="D105" r:id="rId208"/>
+    <hyperlink ref="C106" r:id="rId209"/>
+    <hyperlink ref="D106" r:id="rId210"/>
+    <hyperlink ref="C107" r:id="rId211"/>
+    <hyperlink ref="D107" r:id="rId212"/>
+    <hyperlink ref="C108" r:id="rId213"/>
+    <hyperlink ref="D108" r:id="rId214"/>
+    <hyperlink ref="C109" r:id="rId215"/>
+    <hyperlink ref="D109" r:id="rId216"/>
+    <hyperlink ref="C110" r:id="rId217"/>
+    <hyperlink ref="D110" r:id="rId218"/>
+    <hyperlink ref="C111" r:id="rId219"/>
+    <hyperlink ref="D111" r:id="rId220"/>
+    <hyperlink ref="C112" r:id="rId221"/>
+    <hyperlink ref="D112" r:id="rId222"/>
+    <hyperlink ref="C113" r:id="rId223"/>
+    <hyperlink ref="D113" r:id="rId224"/>
+    <hyperlink ref="C114" r:id="rId225"/>
+    <hyperlink ref="D114" r:id="rId226"/>
+    <hyperlink ref="C115" r:id="rId227"/>
+    <hyperlink ref="D115" r:id="rId228"/>
+    <hyperlink ref="C116" r:id="rId229"/>
+    <hyperlink ref="D116" r:id="rId230"/>
+    <hyperlink ref="C117" r:id="rId231"/>
+    <hyperlink ref="D117" r:id="rId232"/>
+    <hyperlink ref="C118" r:id="rId233"/>
+    <hyperlink ref="D118" r:id="rId234"/>
+    <hyperlink ref="C119" r:id="rId235"/>
+    <hyperlink ref="D119" r:id="rId236"/>
+    <hyperlink ref="C120" r:id="rId237"/>
+    <hyperlink ref="D120" r:id="rId238"/>
+    <hyperlink ref="C121" r:id="rId239"/>
+    <hyperlink ref="D121" r:id="rId240"/>
+    <hyperlink ref="C122" r:id="rId241"/>
+    <hyperlink ref="D122" r:id="rId242"/>
+    <hyperlink ref="C123" r:id="rId243"/>
+    <hyperlink ref="D123" r:id="rId244"/>
+    <hyperlink ref="C124" r:id="rId245"/>
+    <hyperlink ref="D124" r:id="rId246"/>
+    <hyperlink ref="C125" r:id="rId247"/>
+    <hyperlink ref="D125" r:id="rId248"/>
+    <hyperlink ref="C126" r:id="rId249"/>
+    <hyperlink ref="D126" r:id="rId250"/>
+    <hyperlink ref="C127" r:id="rId251"/>
+    <hyperlink ref="D127" r:id="rId252"/>
+    <hyperlink ref="C128" r:id="rId253"/>
+    <hyperlink ref="D128" r:id="rId254"/>
+    <hyperlink ref="C129" r:id="rId255"/>
+    <hyperlink ref="D129" r:id="rId256"/>
+    <hyperlink ref="C130" r:id="rId257"/>
+    <hyperlink ref="D130" r:id="rId258"/>
+    <hyperlink ref="C131" r:id="rId259"/>
+    <hyperlink ref="D131" r:id="rId260"/>
+    <hyperlink ref="C132" r:id="rId261"/>
+    <hyperlink ref="D132" r:id="rId262"/>
+    <hyperlink ref="C133" r:id="rId263"/>
+    <hyperlink ref="D133" r:id="rId264"/>
+    <hyperlink ref="C134" r:id="rId265"/>
+    <hyperlink ref="D134" r:id="rId266"/>
+    <hyperlink ref="C135" r:id="rId267"/>
+    <hyperlink ref="D135" r:id="rId268"/>
+    <hyperlink ref="C136" r:id="rId269"/>
+    <hyperlink ref="D136" r:id="rId270"/>
+    <hyperlink ref="C137" r:id="rId271"/>
+    <hyperlink ref="D137" r:id="rId272"/>
+    <hyperlink ref="C138" r:id="rId273"/>
+    <hyperlink ref="D138" r:id="rId274"/>
+    <hyperlink ref="C139" r:id="rId275"/>
+    <hyperlink ref="D139" r:id="rId276"/>
+    <hyperlink ref="C140" r:id="rId277"/>
+    <hyperlink ref="D140" r:id="rId278"/>
+    <hyperlink ref="C141" r:id="rId279"/>
+    <hyperlink ref="D141" r:id="rId280"/>
+    <hyperlink ref="C142" r:id="rId281"/>
+    <hyperlink ref="D142" r:id="rId282"/>
+    <hyperlink ref="C143" r:id="rId283"/>
+    <hyperlink ref="D143" r:id="rId284"/>
+    <hyperlink ref="C144" r:id="rId285"/>
+    <hyperlink ref="D144" r:id="rId286"/>
+    <hyperlink ref="C145" r:id="rId287"/>
+    <hyperlink ref="D145" r:id="rId288"/>
+    <hyperlink ref="C146" r:id="rId289"/>
+    <hyperlink ref="D146" r:id="rId290"/>
+    <hyperlink ref="C147" r:id="rId291"/>
+    <hyperlink ref="D147" r:id="rId292"/>
+    <hyperlink ref="C148" r:id="rId293"/>
+    <hyperlink ref="D148" r:id="rId294"/>
+    <hyperlink ref="C149" r:id="rId295"/>
+    <hyperlink ref="D149" r:id="rId296"/>
+    <hyperlink ref="C150" r:id="rId297"/>
+    <hyperlink ref="D150" r:id="rId298"/>
+    <hyperlink ref="C151" r:id="rId299"/>
+    <hyperlink ref="D151" r:id="rId300"/>
+    <hyperlink ref="C152" r:id="rId301"/>
+    <hyperlink ref="D152" r:id="rId302"/>
+    <hyperlink ref="C153" r:id="rId303"/>
+    <hyperlink ref="D153" r:id="rId304"/>
+    <hyperlink ref="C154" r:id="rId305"/>
+    <hyperlink ref="D154" r:id="rId306"/>
+    <hyperlink ref="C155" r:id="rId307"/>
+    <hyperlink ref="D155" r:id="rId308"/>
+    <hyperlink ref="C156" r:id="rId309"/>
+    <hyperlink ref="D156" r:id="rId310"/>
+    <hyperlink ref="C157" r:id="rId311"/>
+    <hyperlink ref="D157" r:id="rId312"/>
+    <hyperlink ref="C158" r:id="rId313"/>
+    <hyperlink ref="D158" r:id="rId314"/>
+    <hyperlink ref="C159" r:id="rId315"/>
+    <hyperlink ref="D159" r:id="rId316"/>
+    <hyperlink ref="C160" r:id="rId317"/>
+    <hyperlink ref="D160" r:id="rId318"/>
+    <hyperlink ref="C161" r:id="rId319"/>
+    <hyperlink ref="D161" r:id="rId320"/>
+    <hyperlink ref="C162" r:id="rId321"/>
+    <hyperlink ref="D162" r:id="rId322"/>
+    <hyperlink ref="C163" r:id="rId323"/>
+    <hyperlink ref="D163" r:id="rId324"/>
+    <hyperlink ref="C164" r:id="rId325"/>
+    <hyperlink ref="D164" r:id="rId326"/>
+    <hyperlink ref="C165" r:id="rId327"/>
+    <hyperlink ref="D165" r:id="rId328"/>
+    <hyperlink ref="C166" r:id="rId329"/>
+    <hyperlink ref="D166" r:id="rId330"/>
+    <hyperlink ref="C167" r:id="rId331"/>
+    <hyperlink ref="D167" r:id="rId332"/>
+    <hyperlink ref="C168" r:id="rId333"/>
+    <hyperlink ref="D168" r:id="rId334"/>
+    <hyperlink ref="C169" r:id="rId335"/>
+    <hyperlink ref="D169" r:id="rId336"/>
+    <hyperlink ref="C170" r:id="rId337"/>
+    <hyperlink ref="D170" r:id="rId338"/>
+    <hyperlink ref="C171" r:id="rId339"/>
+    <hyperlink ref="D171" r:id="rId340"/>
+    <hyperlink ref="C172" r:id="rId341"/>
+    <hyperlink ref="D172" r:id="rId342"/>
+    <hyperlink ref="C173" r:id="rId343"/>
+    <hyperlink ref="D173" r:id="rId344"/>
+    <hyperlink ref="C174" r:id="rId345"/>
+    <hyperlink ref="D174" r:id="rId346"/>
+    <hyperlink ref="C175" r:id="rId347"/>
+    <hyperlink ref="D175" r:id="rId348"/>
+    <hyperlink ref="C176" r:id="rId349"/>
+    <hyperlink ref="D176" r:id="rId350"/>
+    <hyperlink ref="C177" r:id="rId351"/>
+    <hyperlink ref="D177" r:id="rId352"/>
+    <hyperlink ref="C178" r:id="rId353"/>
+    <hyperlink ref="D178" r:id="rId354"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>